--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-23</t>
+    <t>2025-11-25</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
   </si>
   <si>
     <t>2025-11-26</t>
@@ -363,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -398,11 +392,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -427,7 +421,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -441,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -475,7 +469,7 @@
         <v>1.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
@@ -483,7 +477,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -497,13 +491,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +519,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -539,7 +533,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -623,7 +617,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -637,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -679,7 +673,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -693,7 +687,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -777,7 +771,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -791,7 +785,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -979,7 +973,7 @@
         <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="45">
@@ -1007,7 +1001,7 @@
         <v>1.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1015,7 +1009,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1029,7 +1023,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1211,7 +1205,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1225,7 +1219,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1267,13 +1261,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="66">
@@ -1281,7 +1275,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1301,7 +1295,7 @@
         <v>1.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1365,13 +1359,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="73">
@@ -1379,7 +1373,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1399,7 +1393,7 @@
         <v>1.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -1407,7 +1401,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1421,7 +1415,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1505,7 +1499,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1519,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1553,34 +1547,6 @@
         <v>1.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1596,21 +1562,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>21.0</v>
@@ -1628,18 +1594,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,259 +28,274 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-25</t>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-11-29</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2025-12-13</t>
+  </si>
+  <si>
+    <t>2025-12-14</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>2025-12-21</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>2025-12-23</t>
+  </si>
+  <si>
+    <t>2025-12-24</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>2025-12-26</t>
+  </si>
+  <si>
+    <t>2025-12-27</t>
+  </si>
+  <si>
+    <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>2026-01-03</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>2026-01-18</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>2026-02-06</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>2026-02-08</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>2025-11-29</t>
-  </si>
-  <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
-  </si>
-  <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
   </si>
   <si>
     <t>Reason</t>
@@ -357,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -378,11 +393,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -390,13 +405,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -404,10 +419,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -418,7 +433,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>23.0</v>
@@ -432,7 +447,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>23.0</v>
@@ -441,15 +456,15 @@
         <v>1.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -460,21 +475,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>24.0</v>
@@ -488,10 +503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -502,10 +517,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -516,7 +531,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>23.0</v>
@@ -530,7 +545,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>23.0</v>
@@ -544,7 +559,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>23.0</v>
@@ -558,7 +573,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>23.0</v>
@@ -572,7 +587,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>23.0</v>
@@ -586,10 +601,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -600,10 +615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -614,7 +629,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>22.0</v>
@@ -628,7 +643,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>22.0</v>
@@ -642,10 +657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -656,10 +671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -670,7 +685,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>23.0</v>
@@ -684,7 +699,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>23.0</v>
@@ -698,7 +713,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>23.0</v>
@@ -712,7 +727,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>23.0</v>
@@ -726,7 +741,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>23.0</v>
@@ -740,10 +755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -754,10 +769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -768,7 +783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>22.0</v>
@@ -782,7 +797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>22.0</v>
@@ -796,7 +811,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>22.0</v>
@@ -810,7 +825,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>22.0</v>
@@ -824,7 +839,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>22.0</v>
@@ -838,7 +853,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>22.0</v>
@@ -852,7 +867,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>22.0</v>
@@ -866,7 +881,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>22.0</v>
@@ -880,7 +895,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>22.0</v>
@@ -894,7 +909,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>22.0</v>
@@ -908,7 +923,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>22.0</v>
@@ -922,7 +937,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>22.0</v>
@@ -936,7 +951,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>22.0</v>
@@ -945,12 +960,12 @@
         <v>1.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>22.0</v>
@@ -964,7 +979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>22.0</v>
@@ -973,15 +988,15 @@
         <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -992,10 +1007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1006,7 +1021,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>21.0</v>
@@ -1020,7 +1035,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>21.0</v>
@@ -1034,7 +1049,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>21.0</v>
@@ -1048,7 +1063,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>21.0</v>
@@ -1062,7 +1077,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>21.0</v>
@@ -1076,7 +1091,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>21.0</v>
@@ -1090,7 +1105,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>21.0</v>
@@ -1104,7 +1119,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>21.0</v>
@@ -1118,7 +1133,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>21.0</v>
@@ -1132,7 +1147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>21.0</v>
@@ -1146,7 +1161,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>21.0</v>
@@ -1160,7 +1175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>21.0</v>
@@ -1174,10 +1189,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1188,10 +1203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1202,7 +1217,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>19.0</v>
@@ -1216,7 +1231,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>19.0</v>
@@ -1230,24 +1245,24 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1258,7 +1273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>20.0</v>
@@ -1267,12 +1282,12 @@
         <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>20.0</v>
@@ -1286,7 +1301,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>20.0</v>
@@ -1300,7 +1315,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>20.0</v>
@@ -1314,7 +1329,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>20.0</v>
@@ -1328,24 +1343,24 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1356,7 +1371,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>21.0</v>
@@ -1365,15 +1380,15 @@
         <v>1.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1384,10 +1399,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1398,7 +1413,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>22.0</v>
@@ -1412,7 +1427,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>22.0</v>
@@ -1426,7 +1441,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>22.0</v>
@@ -1440,7 +1455,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>22.0</v>
@@ -1454,7 +1469,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>22.0</v>
@@ -1468,10 +1483,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
@@ -1482,10 +1497,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1496,7 +1511,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>21.0</v>
@@ -1510,7 +1525,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>21.0</v>
@@ -1524,10 +1539,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1538,16 +1553,86 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B85" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>0.0</v>
+      <c r="B86" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1562,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
@@ -1594,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,12 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
     <t>2025-11-28</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>2026-02-23</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -393,11 +390,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>1.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -405,13 +402,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -419,13 +416,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>1.0</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -433,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>23.0</v>
@@ -442,26 +439,26 @@
         <v>1.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>24.0</v>
@@ -475,7 +472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>24.0</v>
@@ -489,10 +486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -503,7 +500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>23.0</v>
@@ -517,7 +514,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>23.0</v>
@@ -531,7 +528,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>23.0</v>
@@ -545,7 +542,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>23.0</v>
@@ -559,7 +556,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>23.0</v>
@@ -573,7 +570,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>23.0</v>
@@ -587,10 +584,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -601,7 +598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>22.0</v>
@@ -615,7 +612,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>22.0</v>
@@ -629,7 +626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>22.0</v>
@@ -643,10 +640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -657,7 +654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>23.0</v>
@@ -671,7 +668,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>23.0</v>
@@ -685,7 +682,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>23.0</v>
@@ -699,7 +696,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>23.0</v>
@@ -713,7 +710,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>23.0</v>
@@ -727,7 +724,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>23.0</v>
@@ -741,10 +738,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -755,7 +752,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>22.0</v>
@@ -769,7 +766,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>22.0</v>
@@ -783,7 +780,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>22.0</v>
@@ -797,7 +794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>22.0</v>
@@ -811,7 +808,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>22.0</v>
@@ -825,7 +822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>22.0</v>
@@ -839,7 +836,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>22.0</v>
@@ -853,7 +850,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>22.0</v>
@@ -867,7 +864,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>22.0</v>
@@ -881,7 +878,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>22.0</v>
@@ -895,7 +892,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>22.0</v>
@@ -909,7 +906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>22.0</v>
@@ -923,7 +920,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>22.0</v>
@@ -937,7 +934,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>22.0</v>
@@ -946,12 +943,12 @@
         <v>1.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>22.0</v>
@@ -960,12 +957,12 @@
         <v>1.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>22.0</v>
@@ -979,10 +976,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -993,7 +990,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>21.0</v>
@@ -1007,7 +1004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>21.0</v>
@@ -1021,7 +1018,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>21.0</v>
@@ -1035,7 +1032,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>21.0</v>
@@ -1049,7 +1046,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>21.0</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>21.0</v>
@@ -1077,7 +1074,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>21.0</v>
@@ -1091,7 +1088,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>21.0</v>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>21.0</v>
@@ -1119,7 +1116,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>21.0</v>
@@ -1133,7 +1130,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>21.0</v>
@@ -1147,7 +1144,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>21.0</v>
@@ -1161,7 +1158,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>21.0</v>
@@ -1175,10 +1172,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
@@ -1189,7 +1186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>19.0</v>
@@ -1203,7 +1200,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>19.0</v>
@@ -1217,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>19.0</v>
@@ -1231,21 +1228,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>20.0</v>
@@ -1254,12 +1251,12 @@
         <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>20.0</v>
@@ -1273,7 +1270,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>20.0</v>
@@ -1287,7 +1284,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>20.0</v>
@@ -1301,7 +1298,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>20.0</v>
@@ -1315,7 +1312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>20.0</v>
@@ -1329,21 +1326,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>21.0</v>
@@ -1352,12 +1349,12 @@
         <v>1.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>21.0</v>
@@ -1371,10 +1368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1385,7 +1382,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>22.0</v>
@@ -1399,7 +1396,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>22.0</v>
@@ -1413,7 +1410,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>22.0</v>
@@ -1427,7 +1424,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>22.0</v>
@@ -1441,7 +1438,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>22.0</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>22.0</v>
@@ -1469,10 +1466,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
@@ -1483,7 +1480,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>21.0</v>
@@ -1497,7 +1494,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>21.0</v>
@@ -1511,7 +1508,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>21.0</v>
@@ -1525,10 +1522,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1539,7 +1536,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>20.0</v>
@@ -1548,12 +1545,12 @@
         <v>1.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>20.0</v>
@@ -1562,12 +1559,12 @@
         <v>1.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>20.0</v>
@@ -1581,7 +1578,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>20.0</v>
@@ -1595,7 +1592,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>20.0</v>
@@ -1609,7 +1606,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
         <v>20.0</v>
@@ -1619,20 +1616,6 @@
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1647,21 +1630,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>20.0</v>
@@ -1679,18 +1662,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-28</t>
+    <t>2025-11-29</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -369,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -418,14 +415,14 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -433,13 +430,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -573,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -629,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -727,7 +724,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -929,7 +926,7 @@
         <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="41">
@@ -943,7 +940,7 @@
         <v>1.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -965,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -1161,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1217,13 +1214,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="62">
@@ -1237,7 +1234,7 @@
         <v>1.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1315,13 +1312,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="69">
@@ -1335,7 +1332,7 @@
         <v>1.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1357,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1455,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1511,7 +1508,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1531,7 +1528,7 @@
         <v>1.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="84">
@@ -1545,7 +1542,7 @@
         <v>1.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -1601,20 +1598,6 @@
         <v>1.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>20.0</v>
@@ -1662,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,15 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-29</t>
+    <t>2025-11-30</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
     <t>2025-12-01</t>
   </si>
   <si>
@@ -290,6 +287,15 @@
   </si>
   <si>
     <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,14 +407,14 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -416,13 +422,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -458,7 +464,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -556,7 +562,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -612,7 +618,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -710,7 +716,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -912,7 +918,7 @@
         <v>1.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="40">
@@ -926,7 +932,7 @@
         <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -948,7 +954,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -1144,7 +1150,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1200,13 +1206,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="61">
@@ -1220,7 +1226,7 @@
         <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1298,13 +1304,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68">
@@ -1318,7 +1324,7 @@
         <v>1.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1340,7 +1346,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1438,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1494,7 +1500,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1514,7 +1520,7 @@
         <v>1.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="83">
@@ -1528,7 +1534,7 @@
         <v>1.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -1592,13 +1598,41 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1613,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>
@@ -1645,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-30</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-03</t>
@@ -372,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -407,14 +401,14 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -450,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -534,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -548,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -590,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -604,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -688,7 +682,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -702,7 +696,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -890,7 +884,7 @@
         <v>1.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="38">
@@ -918,7 +912,7 @@
         <v>1.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -926,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -940,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -1122,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1136,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1178,13 +1172,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="59">
@@ -1192,7 +1186,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1212,7 +1206,7 @@
         <v>1.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1276,13 +1270,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="66">
@@ -1290,7 +1284,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1310,7 +1304,7 @@
         <v>1.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1318,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1332,7 +1326,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1416,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1430,7 +1424,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1472,7 +1466,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
@@ -1486,13 +1480,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -1520,7 +1514,7 @@
         <v>1.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -1570,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>1.0</v>
@@ -1584,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>1.0</v>
@@ -1605,34 +1599,6 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>19.0</v>
@@ -1679,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-02</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-03</t>
   </si>
   <si>
     <t>2025-12-04</t>
@@ -366,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,11 +398,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,7 +413,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -514,7 +511,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -570,7 +567,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -668,7 +665,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -870,7 +867,7 @@
         <v>1.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="37">
@@ -884,7 +881,7 @@
         <v>1.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -906,7 +903,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -1102,7 +1099,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1158,13 +1155,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="58">
@@ -1178,7 +1175,7 @@
         <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1256,13 +1253,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="65">
@@ -1276,7 +1273,7 @@
         <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1298,7 +1295,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1396,7 +1393,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1452,7 +1449,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1472,7 +1469,7 @@
         <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -1486,7 +1483,7 @@
         <v>1.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -1550,7 +1547,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1584,20 +1581,6 @@
         <v>1.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1613,21 +1596,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>19.0</v>
@@ -1645,18 +1628,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,12 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>2025-12-04</t>
   </si>
   <si>
@@ -287,6 +281,18 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
   </si>
   <si>
     <t>Reason</t>
@@ -363,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -384,11 +390,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -396,10 +402,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>1.0</v>
@@ -410,7 +416,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>23.0</v>
@@ -424,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>23.0</v>
@@ -438,7 +444,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>23.0</v>
@@ -452,7 +458,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>23.0</v>
@@ -466,7 +472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>23.0</v>
@@ -480,7 +486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>23.0</v>
@@ -494,10 +500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -508,7 +514,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>22.0</v>
@@ -522,7 +528,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>22.0</v>
@@ -536,7 +542,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>22.0</v>
@@ -550,10 +556,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -564,7 +570,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>23.0</v>
@@ -578,7 +584,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>23.0</v>
@@ -592,7 +598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>23.0</v>
@@ -606,7 +612,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>23.0</v>
@@ -620,7 +626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>23.0</v>
@@ -634,7 +640,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>23.0</v>
@@ -648,10 +654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -662,7 +668,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>22.0</v>
@@ -676,7 +682,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>22.0</v>
@@ -690,7 +696,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>22.0</v>
@@ -704,7 +710,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>22.0</v>
@@ -718,7 +724,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>22.0</v>
@@ -732,7 +738,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>22.0</v>
@@ -746,7 +752,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>22.0</v>
@@ -760,7 +766,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>22.0</v>
@@ -774,7 +780,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>22.0</v>
@@ -788,7 +794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>22.0</v>
@@ -802,7 +808,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>22.0</v>
@@ -816,7 +822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>22.0</v>
@@ -830,7 +836,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>22.0</v>
@@ -844,7 +850,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>22.0</v>
@@ -853,12 +859,12 @@
         <v>1.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>22.0</v>
@@ -867,12 +873,12 @@
         <v>1.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>22.0</v>
@@ -886,10 +892,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -900,7 +906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>21.0</v>
@@ -914,7 +920,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>21.0</v>
@@ -928,7 +934,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>21.0</v>
@@ -942,7 +948,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>21.0</v>
@@ -956,7 +962,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>21.0</v>
@@ -970,7 +976,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>21.0</v>
@@ -984,7 +990,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>21.0</v>
@@ -998,7 +1004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>21.0</v>
@@ -1012,7 +1018,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>21.0</v>
@@ -1026,7 +1032,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>21.0</v>
@@ -1040,7 +1046,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>21.0</v>
@@ -1054,7 +1060,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>21.0</v>
@@ -1068,7 +1074,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>21.0</v>
@@ -1082,10 +1088,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1096,7 +1102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>19.0</v>
@@ -1110,7 +1116,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>19.0</v>
@@ -1124,7 +1130,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>19.0</v>
@@ -1138,21 +1144,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>20.0</v>
@@ -1161,12 +1167,12 @@
         <v>1.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>20.0</v>
@@ -1180,7 +1186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>20.0</v>
@@ -1194,7 +1200,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>20.0</v>
@@ -1208,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>20.0</v>
@@ -1222,7 +1228,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>20.0</v>
@@ -1236,21 +1242,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>21.0</v>
@@ -1259,12 +1265,12 @@
         <v>1.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>21.0</v>
@@ -1278,10 +1284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1292,7 +1298,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>22.0</v>
@@ -1306,7 +1312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>22.0</v>
@@ -1320,7 +1326,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>22.0</v>
@@ -1334,7 +1340,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>22.0</v>
@@ -1348,7 +1354,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>22.0</v>
@@ -1362,7 +1368,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>22.0</v>
@@ -1376,10 +1382,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1390,7 +1396,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>21.0</v>
@@ -1404,7 +1410,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>21.0</v>
@@ -1418,7 +1424,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>21.0</v>
@@ -1432,10 +1438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1446,7 +1452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>20.0</v>
@@ -1455,12 +1461,12 @@
         <v>1.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>20.0</v>
@@ -1469,12 +1475,12 @@
         <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>20.0</v>
@@ -1488,7 +1494,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>20.0</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>20.0</v>
@@ -1516,7 +1522,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>20.0</v>
@@ -1530,10 +1536,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1544,7 +1550,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>19.0</v>
@@ -1558,7 +1564,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>19.0</v>
@@ -1572,7 +1578,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>19.0</v>
@@ -1581,6 +1587,48 @@
         <v>1.0</v>
       </c>
       <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1596,21 +1644,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>19.0</v>
@@ -1628,18 +1676,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
     <t>2025-12-06</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2025-12-07</t>
@@ -369,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -390,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>1.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -402,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,7 +413,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>23.0</v>
@@ -430,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>23.0</v>
@@ -444,7 +441,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>23.0</v>
@@ -458,7 +455,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>23.0</v>
@@ -472,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -486,10 +483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -500,7 +497,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>22.0</v>
@@ -514,7 +511,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>22.0</v>
@@ -528,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -542,10 +539,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -556,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>23.0</v>
@@ -570,7 +567,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>23.0</v>
@@ -584,7 +581,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>23.0</v>
@@ -598,7 +595,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>23.0</v>
@@ -612,7 +609,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>23.0</v>
@@ -626,10 +623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -640,10 +637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -654,7 +651,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>22.0</v>
@@ -668,7 +665,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>22.0</v>
@@ -682,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>22.0</v>
@@ -696,7 +693,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>22.0</v>
@@ -710,7 +707,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>22.0</v>
@@ -724,7 +721,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>22.0</v>
@@ -738,7 +735,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>22.0</v>
@@ -752,7 +749,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>22.0</v>
@@ -766,7 +763,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>22.0</v>
@@ -780,7 +777,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>22.0</v>
@@ -794,7 +791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>22.0</v>
@@ -808,7 +805,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>22.0</v>
@@ -822,7 +819,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>22.0</v>
@@ -831,12 +828,12 @@
         <v>1.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>22.0</v>
@@ -850,7 +847,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>22.0</v>
@@ -859,15 +856,15 @@
         <v>1.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -878,10 +875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -892,7 +889,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>21.0</v>
@@ -906,7 +903,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>21.0</v>
@@ -920,7 +917,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>21.0</v>
@@ -934,7 +931,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>21.0</v>
@@ -948,7 +945,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>21.0</v>
@@ -962,7 +959,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>21.0</v>
@@ -976,7 +973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>21.0</v>
@@ -990,7 +987,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>21.0</v>
@@ -1004,7 +1001,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>21.0</v>
@@ -1018,7 +1015,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>21.0</v>
@@ -1032,7 +1029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>21.0</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>21.0</v>
@@ -1060,10 +1057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1074,10 +1071,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
@@ -1088,7 +1085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>19.0</v>
@@ -1102,7 +1099,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>19.0</v>
@@ -1116,24 +1113,24 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1144,7 +1141,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>20.0</v>
@@ -1153,12 +1150,12 @@
         <v>1.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>20.0</v>
@@ -1172,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>20.0</v>
@@ -1186,7 +1183,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>20.0</v>
@@ -1200,7 +1197,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>20.0</v>
@@ -1214,24 +1211,24 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1242,7 +1239,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>21.0</v>
@@ -1251,15 +1248,15 @@
         <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1270,10 +1267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1284,7 +1281,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>22.0</v>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>22.0</v>
@@ -1312,7 +1309,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>22.0</v>
@@ -1326,7 +1323,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>22.0</v>
@@ -1340,7 +1337,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>22.0</v>
@@ -1354,10 +1351,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1368,10 +1365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>21.0</v>
@@ -1396,7 +1393,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>21.0</v>
@@ -1410,10 +1407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1424,21 +1421,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>20.0</v>
@@ -1452,7 +1449,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>20.0</v>
@@ -1461,12 +1458,12 @@
         <v>1.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>20.0</v>
@@ -1480,7 +1477,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>20.0</v>
@@ -1494,7 +1491,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>20.0</v>
@@ -1508,10 +1505,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1522,10 +1519,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1536,7 +1533,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>19.0</v>
@@ -1550,7 +1547,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>19.0</v>
@@ -1564,7 +1561,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>19.0</v>
@@ -1578,7 +1575,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>19.0</v>
@@ -1592,7 +1589,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>19.0</v>
@@ -1601,34 +1598,6 @@
         <v>1.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1644,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>19.0</v>
@@ -1676,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -28,42 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-16</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
     <t>2025-12-17</t>
   </si>
   <si>
@@ -290,6 +260,36 @@
   </si>
   <si>
     <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Reason</t>
@@ -472,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -528,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -542,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -570,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -598,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -612,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -688,7 +688,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -724,7 +724,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -738,7 +738,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -752,7 +752,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -766,7 +766,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -780,7 +780,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -794,7 +794,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -808,7 +808,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -822,13 +822,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -836,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -850,7 +850,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -920,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -934,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -948,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -976,13 +976,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="45">
@@ -990,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1018,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1032,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1046,7 +1046,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1060,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1074,13 +1074,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="52">
@@ -1088,7 +1088,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1102,7 +1102,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1116,13 +1116,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1130,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1144,7 +1144,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1158,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1172,7 +1172,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
@@ -1186,7 +1186,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1200,7 +1200,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1220,7 +1220,7 @@
         <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1256,7 +1256,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1270,7 +1270,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1284,13 +1284,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="67">
@@ -1298,7 +1298,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1312,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1326,7 +1326,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1340,7 +1340,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1354,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1368,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1382,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1396,7 +1396,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1410,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1424,13 +1424,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -1438,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1452,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1466,13 +1466,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -1480,7 +1480,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
@@ -1494,7 +1494,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1508,7 +1508,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1522,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1536,7 +1536,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1550,7 +1550,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1564,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>1.0</v>
@@ -1592,7 +1592,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>1.0</v>
@@ -1630,7 +1630,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -28,75 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-16</t>
+    <t>2026-01-06</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
     <t>2026-01-07</t>
   </si>
   <si>
@@ -290,6 +227,69 @@
   </si>
   <si>
     <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
   </si>
   <si>
     <t>Reason</t>
@@ -394,7 +394,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -416,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -430,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -444,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -458,7 +458,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -472,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -486,7 +486,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -500,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -514,7 +514,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -528,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -542,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -570,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -598,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -612,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -626,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -640,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -668,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -682,7 +682,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -696,7 +696,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -724,7 +724,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -738,7 +738,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -752,7 +752,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -766,7 +766,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -786,7 +786,7 @@
         <v>1.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
@@ -822,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -836,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -850,7 +850,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -864,7 +864,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -878,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -892,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -906,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -920,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -934,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -948,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -982,7 +982,7 @@
         <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -996,7 +996,7 @@
         <v>1.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="46">
@@ -1074,13 +1074,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1088,7 +1088,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1102,7 +1102,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1116,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1130,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1144,7 +1144,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1158,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1172,13 +1172,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="59">
@@ -1186,7 +1186,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1200,7 +1200,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1214,7 +1214,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1228,7 +1228,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1242,7 +1242,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
@@ -1256,7 +1256,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1270,7 +1270,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1284,13 +1284,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1298,7 +1298,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1312,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1326,7 +1326,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1340,7 +1340,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1354,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1368,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1382,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1396,7 +1396,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1410,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1424,7 +1424,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1438,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1452,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1466,13 +1466,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -1480,7 +1480,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
@@ -1494,7 +1494,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1508,7 +1508,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1522,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1536,7 +1536,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1550,7 +1550,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1564,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>1.0</v>
@@ -1578,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>1.0</v>
@@ -1592,7 +1592,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>1.0</v>
@@ -1630,7 +1630,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-06</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
     <t>2026-01-12</t>
   </si>
   <si>
@@ -290,6 +275,27 @@
   </si>
   <si>
     <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -394,18 +400,18 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,7 +422,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -556,7 +562,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -570,7 +576,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -584,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -598,7 +604,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -612,13 +618,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -626,7 +632,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -640,7 +646,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -654,7 +660,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -668,7 +674,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -688,7 +694,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -710,13 +716,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
@@ -724,7 +730,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -738,7 +744,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -752,7 +758,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -766,7 +772,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -780,13 +786,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -794,7 +800,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -808,7 +814,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -850,7 +856,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -864,7 +870,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -878,7 +884,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -892,7 +898,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -906,7 +912,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -920,13 +926,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="41">
@@ -934,7 +940,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -948,7 +954,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -962,7 +968,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -996,7 +1002,7 @@
         <v>1.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1004,7 +1010,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1018,7 +1024,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1032,7 +1038,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1046,7 +1052,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1060,7 +1066,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1102,13 +1108,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
@@ -1116,7 +1122,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1130,7 +1136,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1144,7 +1150,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1158,7 +1164,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1172,13 +1178,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1186,7 +1192,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1200,7 +1206,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1214,7 +1220,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1228,7 +1234,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1270,7 +1276,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1284,7 +1290,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1298,7 +1304,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1340,7 +1346,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1354,7 +1360,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1368,7 +1374,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1382,7 +1388,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1396,7 +1402,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1410,7 +1416,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1424,7 +1430,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1438,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1452,7 +1458,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1466,7 +1472,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
@@ -1480,7 +1486,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
@@ -1494,7 +1500,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1508,7 +1514,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1522,7 +1528,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1536,7 +1542,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1550,7 +1556,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1592,12 +1598,40 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1613,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>
@@ -1645,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,51 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-24</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
     <t>2026-01-25</t>
   </si>
   <si>
@@ -296,6 +257,48 @@
   </si>
   <si>
     <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -407,11 +410,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -422,7 +425,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -436,13 +439,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -450,7 +453,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -464,7 +467,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -478,7 +481,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -492,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -506,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -520,7 +523,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -540,7 +543,7 @@
         <v>1.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -562,7 +565,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -576,7 +579,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -590,7 +593,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -604,7 +607,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -618,13 +621,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -632,7 +635,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -646,7 +649,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -660,7 +663,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -674,7 +677,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -688,7 +691,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -702,7 +705,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -722,7 +725,7 @@
         <v>1.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -730,7 +733,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -744,13 +747,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +761,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -772,7 +775,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -786,7 +789,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -800,7 +803,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -814,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -828,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -842,7 +845,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -856,7 +859,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -870,7 +873,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -884,7 +887,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -898,7 +901,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -912,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -926,7 +929,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -940,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -954,7 +957,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -968,7 +971,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -982,7 +985,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -996,7 +999,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -1010,7 +1013,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1024,7 +1027,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1038,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1052,7 +1055,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1066,7 +1069,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1080,7 +1083,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
@@ -1094,7 +1097,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1108,13 +1111,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1122,7 +1125,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1136,7 +1139,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1164,7 +1167,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1178,7 +1181,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
@@ -1192,7 +1195,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1220,7 +1223,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1234,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1248,7 +1251,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
@@ -1262,7 +1265,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1276,7 +1279,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1290,7 +1293,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1304,7 +1307,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1318,7 +1321,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1332,7 +1335,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1346,7 +1349,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1360,7 +1363,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1374,7 +1377,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1388,7 +1391,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1402,7 +1405,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1416,10 +1419,10 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D75" t="n" s="0">
         <v>0.0</v>
@@ -1430,10 +1433,10 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1447,7 +1450,7 @@
         <v>19.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D77" t="n" s="0">
         <v>0.0</v>
@@ -1458,10 +1461,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1472,10 +1475,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D79" t="n" s="0">
         <v>0.0</v>
@@ -1486,10 +1489,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D80" t="n" s="0">
         <v>0.0</v>
@@ -1500,10 +1503,10 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D81" t="n" s="0">
         <v>0.0</v>
@@ -1514,10 +1517,10 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D82" t="n" s="0">
         <v>0.0</v>
@@ -1528,10 +1531,10 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D83" t="n" s="0">
         <v>0.0</v>
@@ -1542,10 +1545,10 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D84" t="n" s="0">
         <v>0.0</v>
@@ -1556,10 +1559,10 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D85" t="n" s="0">
         <v>0.0</v>
@@ -1570,10 +1573,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D86" t="n" s="0">
         <v>0.0</v>
@@ -1584,10 +1587,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D87" t="n" s="0">
         <v>0.0</v>
@@ -1598,7 +1601,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1612,7 +1615,7 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
@@ -1626,13 +1629,27 @@
         <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C90" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D90" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,24 +1664,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
@@ -1679,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,87 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-24</t>
+    <t>2026-02-18</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
     <t>2026-02-19</t>
   </si>
   <si>
@@ -299,6 +224,81 @@
   </si>
   <si>
     <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
   </si>
   <si>
     <t>Reason</t>
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,11 +424,11 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>1.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -438,25 +438,25 @@
       <c r="A5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B5" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>1.0</v>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B6" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>1.0</v>
+      <c r="B6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -481,7 +481,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -495,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -509,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -523,7 +523,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -537,13 +537,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -565,7 +565,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -579,13 +579,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -607,7 +607,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -621,7 +621,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -635,7 +635,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -649,7 +649,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -663,7 +663,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -677,7 +677,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -691,7 +691,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -705,7 +705,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -719,7 +719,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -733,7 +733,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -747,13 +747,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -761,7 +761,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -775,7 +775,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -789,7 +789,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -803,7 +803,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -817,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -831,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -845,7 +845,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -859,7 +859,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -873,7 +873,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -887,7 +887,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -901,7 +901,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -929,13 +929,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -957,7 +957,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -971,7 +971,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -985,7 +985,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -999,7 +999,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -1013,7 +1013,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1027,7 +1027,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1055,7 +1055,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1069,10 +1069,10 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1083,10 +1083,10 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1097,10 +1097,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D52" t="n" s="0">
         <v>0.0</v>
@@ -1111,10 +1111,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D53" t="n" s="0">
         <v>0.0</v>
@@ -1125,10 +1125,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D54" t="n" s="0">
         <v>0.0</v>
@@ -1139,10 +1139,10 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D55" t="n" s="0">
         <v>0.0</v>
@@ -1153,10 +1153,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D56" t="n" s="0">
         <v>0.0</v>
@@ -1167,10 +1167,10 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D57" t="n" s="0">
         <v>0.0</v>
@@ -1181,10 +1181,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D58" t="n" s="0">
         <v>0.0</v>
@@ -1195,10 +1195,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D59" t="n" s="0">
         <v>0.0</v>
@@ -1209,10 +1209,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D60" t="n" s="0">
         <v>0.0</v>
@@ -1223,10 +1223,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1237,10 +1237,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1251,10 +1251,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D63" t="n" s="0">
         <v>0.0</v>
@@ -1265,10 +1265,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D64" t="n" s="0">
         <v>0.0</v>
@@ -1279,10 +1279,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D65" t="n" s="0">
         <v>0.0</v>
@@ -1293,10 +1293,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D66" t="n" s="0">
         <v>0.0</v>
@@ -1310,7 +1310,7 @@
         <v>19.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1321,10 +1321,10 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D68" t="n" s="0">
         <v>0.0</v>
@@ -1335,10 +1335,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D69" t="n" s="0">
         <v>0.0</v>
@@ -1349,10 +1349,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D70" t="n" s="0">
         <v>0.0</v>
@@ -1363,10 +1363,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D71" t="n" s="0">
         <v>0.0</v>
@@ -1377,10 +1377,10 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D72" t="n" s="0">
         <v>0.0</v>
@@ -1391,10 +1391,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D73" t="n" s="0">
         <v>0.0</v>
@@ -1405,10 +1405,10 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D74" t="n" s="0">
         <v>0.0</v>
@@ -1461,7 +1461,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1475,7 +1475,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1489,7 +1489,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1503,7 +1503,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1517,7 +1517,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1531,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1545,7 +1545,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1559,10 +1559,10 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D85" t="n" s="0">
         <v>0.0</v>
@@ -1573,10 +1573,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D86" t="n" s="0">
         <v>0.0</v>
@@ -1587,10 +1587,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D87" t="n" s="0">
         <v>0.0</v>
@@ -1601,10 +1601,10 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
@@ -1615,10 +1615,10 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
@@ -1629,10 +1629,10 @@
         <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D90" t="n" s="0">
         <v>0.0</v>
@@ -1643,10 +1643,10 @@
         <v>94</v>
       </c>
       <c r="B91" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D91" t="s" s="0">
         <v>5</v>
@@ -1681,7 +1681,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,45 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>2026-03-02</t>
   </si>
   <si>
@@ -299,6 +260,36 @@
   </si>
   <si>
     <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
   </si>
   <si>
     <t>Reason</t>
@@ -375,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -396,39 +387,39 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -436,13 +427,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -450,13 +441,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -464,10 +455,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -478,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -492,10 +483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -506,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -520,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -534,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -548,10 +539,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -562,10 +553,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -576,24 +567,24 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -604,10 +595,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -618,7 +609,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>15.0</v>
@@ -632,7 +623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>15.0</v>
@@ -646,10 +637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -660,10 +651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -674,7 +665,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>16.0</v>
@@ -688,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>16.0</v>
@@ -702,10 +693,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -716,10 +707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -730,10 +721,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -744,10 +735,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -758,10 +749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -772,10 +763,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -800,10 +791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -814,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -828,10 +819,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -842,10 +833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -856,10 +847,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -870,10 +861,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -884,10 +875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -898,13 +889,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D38" t="n" s="0">
         <v>0.0</v>
@@ -912,13 +903,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>19.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D39" t="n" s="0">
         <v>0.0</v>
@@ -926,13 +917,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>19.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D40" t="n" s="0">
         <v>0.0</v>
@@ -940,13 +931,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D41" t="n" s="0">
         <v>0.0</v>
@@ -954,13 +945,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D42" t="n" s="0">
         <v>0.0</v>
@@ -968,13 +959,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D43" t="n" s="0">
         <v>0.0</v>
@@ -982,13 +973,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D44" t="n" s="0">
         <v>0.0</v>
@@ -996,13 +987,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D45" t="n" s="0">
         <v>0.0</v>
@@ -1010,13 +1001,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D46" t="n" s="0">
         <v>0.0</v>
@@ -1024,13 +1015,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D47" t="n" s="0">
         <v>0.0</v>
@@ -1038,13 +1029,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>0.0</v>
@@ -1052,13 +1043,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D49" t="n" s="0">
         <v>0.0</v>
@@ -1066,10 +1057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1080,10 +1071,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1094,10 +1085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1108,7 +1099,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>20.0</v>
@@ -1122,7 +1113,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>20.0</v>
@@ -1136,10 +1127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1150,10 +1141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1164,10 +1155,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1178,10 +1169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1192,10 +1183,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1206,10 +1197,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1220,10 +1211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1234,10 +1225,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1248,10 +1239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1262,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1276,10 +1267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1290,10 +1281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1304,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1318,10 +1309,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1332,10 +1323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1346,10 +1337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1360,10 +1351,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1374,10 +1365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1388,13 +1379,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D73" t="n" s="0">
         <v>0.0</v>
@@ -1402,13 +1393,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D74" t="n" s="0">
         <v>0.0</v>
@@ -1416,13 +1407,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D75" t="n" s="0">
         <v>0.0</v>
@@ -1430,13 +1421,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>19.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1444,13 +1435,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>19.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D77" t="n" s="0">
         <v>0.0</v>
@@ -1458,13 +1449,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1472,13 +1463,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
         <v>0.0</v>
@@ -1486,13 +1477,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>17.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D80" t="n" s="0">
         <v>0.0</v>
@@ -1500,13 +1491,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D81" t="n" s="0">
         <v>0.0</v>
@@ -1514,13 +1505,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D82" t="n" s="0">
         <v>0.0</v>
@@ -1528,13 +1519,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D83" t="n" s="0">
         <v>0.0</v>
@@ -1542,13 +1533,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D84" t="n" s="0">
         <v>0.0</v>
@@ -1556,10 +1547,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1570,10 +1561,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>1.0</v>
@@ -1584,7 +1575,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>18.0</v>
@@ -1598,10 +1589,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>1.0</v>
@@ -1612,44 +1603,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1664,24 +1627,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
     </row>
   </sheetData>
@@ -1696,18 +1659,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,24 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2026-03-07</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-03-08</t>
   </si>
   <si>
@@ -290,6 +278,27 @@
   </si>
   <si>
     <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +396,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>1.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,24 +408,24 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -427,10 +436,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -441,10 +450,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -455,10 +464,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -469,7 +478,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>15.0</v>
@@ -483,7 +492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>15.0</v>
@@ -497,10 +506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -511,10 +520,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -525,10 +534,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -539,7 +548,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>15.0</v>
@@ -553,7 +562,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>15.0</v>
@@ -567,10 +576,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -581,10 +590,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -595,10 +604,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -609,10 +618,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -623,10 +632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -637,10 +646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -651,10 +660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -665,10 +674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -679,10 +688,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -693,10 +702,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -707,10 +716,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -721,10 +730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -735,10 +744,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -749,10 +758,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -763,10 +772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -791,7 +800,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>18.0</v>
@@ -805,7 +814,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>18.0</v>
@@ -819,13 +828,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D33" t="n" s="0">
         <v>0.0</v>
@@ -833,13 +842,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" t="n" s="0">
         <v>0.0</v>
@@ -847,13 +856,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D35" t="n" s="0">
         <v>0.0</v>
@@ -861,13 +870,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D36" t="n" s="0">
         <v>0.0</v>
@@ -875,13 +884,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" t="n" s="0">
         <v>0.0</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -903,10 +912,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -917,10 +926,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -931,7 +940,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>20.0</v>
@@ -945,7 +954,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>20.0</v>
@@ -959,7 +968,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>20.0</v>
@@ -973,7 +982,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>20.0</v>
@@ -987,7 +996,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>20.0</v>
@@ -1001,7 +1010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>20.0</v>
@@ -1015,7 +1024,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>20.0</v>
@@ -1029,7 +1038,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>20.0</v>
@@ -1043,7 +1052,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>20.0</v>
@@ -1057,10 +1066,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1071,10 +1080,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1085,10 +1094,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1127,7 +1136,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>19.0</v>
@@ -1141,7 +1150,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>19.0</v>
@@ -1155,7 +1164,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>19.0</v>
@@ -1169,7 +1178,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>19.0</v>
@@ -1183,7 +1192,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>19.0</v>
@@ -1197,7 +1206,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>19.0</v>
@@ -1211,10 +1220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,10 +1234,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1239,10 +1248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1253,10 +1262,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1267,10 +1276,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1281,10 +1290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1295,10 +1304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,13 +1318,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D68" t="n" s="0">
         <v>0.0</v>
@@ -1323,13 +1332,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D69" t="n" s="0">
         <v>0.0</v>
@@ -1337,13 +1346,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D70" t="n" s="0">
         <v>0.0</v>
@@ -1351,13 +1360,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D71" t="n" s="0">
         <v>0.0</v>
@@ -1365,13 +1374,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1388,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1393,10 +1402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1407,10 +1416,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1421,10 +1430,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1435,10 +1444,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1449,10 +1458,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1463,10 +1472,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
@@ -1477,7 +1486,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>17.0</v>
@@ -1491,7 +1500,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>17.0</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1519,10 +1528,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1533,10 +1542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>1.0</v>
@@ -1547,10 +1556,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>1.0</v>
@@ -1561,10 +1570,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>1.0</v>
@@ -1575,7 +1584,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>18.0</v>
@@ -1589,7 +1598,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>18.0</v>
@@ -1603,16 +1612,44 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
+      <c r="D89" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1627,24 +1664,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
     </row>
   </sheetData>
@@ -1659,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,36 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-07</t>
+    <t>2026-03-15</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>2026-03-16</t>
   </si>
   <si>
@@ -299,6 +275,27 @@
   </si>
   <si>
     <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
   </si>
   <si>
     <t>Reason</t>
@@ -375,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,11 +407,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -439,7 +436,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -453,7 +450,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -481,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -495,7 +492,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -509,7 +506,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -523,7 +520,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -537,7 +534,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -551,7 +548,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -565,7 +562,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -579,7 +576,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -593,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -607,7 +604,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -621,7 +618,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -635,7 +632,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -649,7 +646,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -663,7 +660,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -677,7 +674,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -691,7 +688,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -705,7 +702,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -722,7 +719,7 @@
         <v>19.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D25" t="n" s="0">
         <v>0.0</v>
@@ -733,10 +730,10 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D26" t="n" s="0">
         <v>0.0</v>
@@ -747,10 +744,10 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D27" t="n" s="0">
         <v>0.0</v>
@@ -761,10 +758,10 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D28" t="n" s="0">
         <v>0.0</v>
@@ -775,10 +772,10 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>0.0</v>
@@ -789,10 +786,10 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D30" t="n" s="0">
         <v>0.0</v>
@@ -803,10 +800,10 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D31" t="n" s="0">
         <v>0.0</v>
@@ -817,10 +814,10 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D32" t="n" s="0">
         <v>0.0</v>
@@ -831,7 +828,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -845,7 +842,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -859,7 +856,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -957,7 +954,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -971,7 +968,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -985,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -999,7 +996,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1013,7 +1010,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1027,7 +1024,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1041,7 +1038,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1055,7 +1052,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1111,7 +1108,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1125,7 +1122,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1139,7 +1136,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1153,7 +1150,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1167,7 +1164,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1181,7 +1178,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1195,7 +1192,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1209,10 +1206,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D60" t="n" s="0">
         <v>0.0</v>
@@ -1223,10 +1220,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1237,10 +1234,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1251,10 +1248,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
         <v>0.0</v>
@@ -1265,10 +1262,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D64" t="n" s="0">
         <v>0.0</v>
@@ -1279,10 +1276,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
         <v>0.0</v>
@@ -1293,10 +1290,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D66" t="n" s="0">
         <v>0.0</v>
@@ -1307,10 +1304,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1321,7 +1318,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1335,7 +1332,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1349,7 +1346,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1363,7 +1360,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1377,7 +1374,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1391,7 +1388,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1405,7 +1402,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>1.0</v>
@@ -1419,7 +1416,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>1.0</v>
@@ -1433,7 +1430,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>1.0</v>
@@ -1447,7 +1444,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>1.0</v>
@@ -1461,7 +1458,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>1.0</v>
@@ -1475,7 +1472,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>1.0</v>
@@ -1489,7 +1486,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>1.0</v>
@@ -1517,7 +1514,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1531,7 +1528,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1615,13 +1612,13 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="D89" t="s" s="0">
-        <v>5</v>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -1629,27 +1626,13 @@
         <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C90" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
+      <c r="D90" t="n" s="0">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1664,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="C2" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
   </sheetData>
@@ -1696,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>102</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,42 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-15</t>
+    <t>2026-03-25</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
     <t>2026-03-26</t>
   </si>
   <si>
@@ -296,6 +266,39 @@
   </si>
   <si>
     <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -408,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>1.0</v>
@@ -422,7 +425,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -436,7 +439,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -450,7 +453,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -464,7 +467,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -478,7 +481,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -492,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -506,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -520,7 +523,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -534,7 +537,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -548,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -562,7 +565,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -579,7 +582,7 @@
         <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D15" t="n" s="0">
         <v>0.0</v>
@@ -593,7 +596,7 @@
         <v>19.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D16" t="n" s="0">
         <v>0.0</v>
@@ -607,7 +610,7 @@
         <v>19.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D17" t="n" s="0">
         <v>0.0</v>
@@ -618,10 +621,10 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D18" t="n" s="0">
         <v>0.0</v>
@@ -632,10 +635,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D19" t="n" s="0">
         <v>0.0</v>
@@ -646,10 +649,10 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" t="n" s="0">
         <v>0.0</v>
@@ -660,10 +663,10 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D21" t="n" s="0">
         <v>0.0</v>
@@ -674,10 +677,10 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>0.0</v>
@@ -688,10 +691,10 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D23" t="n" s="0">
         <v>0.0</v>
@@ -702,10 +705,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D24" t="n" s="0">
         <v>0.0</v>
@@ -716,7 +719,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -730,7 +733,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -744,7 +747,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -814,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -828,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -842,7 +845,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -856,7 +859,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -870,7 +873,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -884,7 +887,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -898,7 +901,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -912,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -926,7 +929,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -940,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -968,7 +971,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -982,7 +985,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -996,7 +999,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1010,7 +1013,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1024,7 +1027,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1038,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1052,7 +1055,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1066,10 +1069,10 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1080,10 +1083,10 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1094,10 +1097,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D52" t="n" s="0">
         <v>0.0</v>
@@ -1108,10 +1111,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D53" t="n" s="0">
         <v>0.0</v>
@@ -1122,10 +1125,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D54" t="n" s="0">
         <v>0.0</v>
@@ -1136,10 +1139,10 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D55" t="n" s="0">
         <v>0.0</v>
@@ -1150,10 +1153,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D56" t="n" s="0">
         <v>0.0</v>
@@ -1164,10 +1167,10 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D57" t="n" s="0">
         <v>0.0</v>
@@ -1178,10 +1181,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
         <v>0.0</v>
@@ -1192,10 +1195,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D59" t="n" s="0">
         <v>0.0</v>
@@ -1206,7 +1209,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1220,7 +1223,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1234,7 +1237,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1248,7 +1251,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
@@ -1262,7 +1265,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>1.0</v>
@@ -1276,7 +1279,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1290,7 +1293,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1304,7 +1307,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1318,7 +1321,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>1.0</v>
@@ -1332,7 +1335,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>1.0</v>
@@ -1346,7 +1349,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>1.0</v>
@@ -1500,7 +1503,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>1.0</v>
@@ -1514,7 +1517,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>1.0</v>
@@ -1528,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>1.0</v>
@@ -1556,10 +1559,10 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D85" t="n" s="0">
         <v>0.0</v>
@@ -1570,10 +1573,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D86" t="n" s="0">
         <v>0.0</v>
@@ -1584,10 +1587,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D87" t="n" s="0">
         <v>0.0</v>
@@ -1601,7 +1604,7 @@
         <v>18.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
@@ -1615,7 +1618,7 @@
         <v>18.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
@@ -1629,10 +1632,24 @@
         <v>18.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D90" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,21 +1664,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>18.0</v>
@@ -1679,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,30 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-25</t>
+    <t>2026-03-31</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
     <t>2026-04-01</t>
   </si>
   <si>
@@ -299,6 +281,15 @@
   </si>
   <si>
     <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
   </si>
   <si>
     <t>Reason</t>
@@ -375,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,11 +401,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -425,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -439,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -453,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -467,7 +458,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -495,10 +486,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -509,10 +500,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D10" t="n" s="0">
         <v>0.0</v>
@@ -523,10 +514,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D11" t="n" s="0">
         <v>0.0</v>
@@ -537,10 +528,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D12" t="n" s="0">
         <v>0.0</v>
@@ -551,10 +542,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D13" t="n" s="0">
         <v>0.0</v>
@@ -565,10 +556,10 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D14" t="n" s="0">
         <v>0.0</v>
@@ -579,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -593,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -607,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -733,7 +724,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -747,7 +738,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -761,7 +752,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -775,7 +766,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -789,7 +780,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -803,7 +794,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -887,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -901,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -915,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -929,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -943,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -957,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -971,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -985,10 +976,10 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
         <v>0.0</v>
@@ -999,10 +990,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D45" t="n" s="0">
         <v>0.0</v>
@@ -1016,7 +1007,7 @@
         <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D46" t="n" s="0">
         <v>0.0</v>
@@ -1027,10 +1018,10 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D47" t="n" s="0">
         <v>0.0</v>
@@ -1041,10 +1032,10 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>0.0</v>
@@ -1055,10 +1046,10 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D49" t="n" s="0">
         <v>0.0</v>
@@ -1069,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1083,7 +1074,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
@@ -1097,7 +1088,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1111,7 +1102,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1125,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1139,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1153,7 +1144,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1181,7 +1172,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
@@ -1195,7 +1186,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1209,7 +1200,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1223,7 +1214,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1237,7 +1228,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>1.0</v>
@@ -1251,7 +1242,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>1.0</v>
@@ -1279,7 +1270,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1293,7 +1284,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1307,7 +1298,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1363,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>1.0</v>
@@ -1377,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>1.0</v>
@@ -1391,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>1.0</v>
@@ -1475,10 +1466,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D79" t="n" s="0">
         <v>0.0</v>
@@ -1489,10 +1480,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D80" t="n" s="0">
         <v>0.0</v>
@@ -1503,10 +1494,10 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D81" t="n" s="0">
         <v>0.0</v>
@@ -1520,7 +1511,7 @@
         <v>18.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D82" t="n" s="0">
         <v>0.0</v>
@@ -1534,7 +1525,7 @@
         <v>18.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D83" t="n" s="0">
         <v>0.0</v>
@@ -1548,7 +1539,7 @@
         <v>18.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D84" t="n" s="0">
         <v>0.0</v>
@@ -1559,7 +1550,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1573,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1587,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1608,48 +1599,6 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1664,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>18.0</v>
@@ -1696,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
     <t>2026-04-06</t>
   </si>
   <si>
@@ -290,6 +269,27 @@
   </si>
   <si>
     <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -413,13 +413,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -427,13 +427,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -455,13 +455,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>0.0</v>
@@ -469,13 +469,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -483,10 +483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -497,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>20.0</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>20.0</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>20.0</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>20.0</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>20.0</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>20.0</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>20.0</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>20.0</v>
@@ -637,10 +637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -651,10 +651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -679,10 +679,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -693,10 +693,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -707,10 +707,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>19.0</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>19.0</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>19.0</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>19.0</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>19.0</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -833,10 +833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -847,10 +847,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -875,10 +875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -889,13 +889,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D38" t="n" s="0">
         <v>0.0</v>
@@ -903,13 +903,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D39" t="n" s="0">
         <v>0.0</v>
@@ -917,13 +917,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
         <v>0.0</v>
@@ -931,13 +931,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D41" t="n" s="0">
         <v>0.0</v>
@@ -945,13 +945,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D42" t="n" s="0">
         <v>0.0</v>
@@ -959,13 +959,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D43" t="n" s="0">
         <v>0.0</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>17.0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>1.0</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>1.0</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>1.0</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>18.0</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>18.0</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>18.0</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>18.0</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>1.0</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>1.0</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>1.0</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>18.0</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>18.0</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>18.0</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>18.0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>18.0</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D73" t="n" s="0">
         <v>0.0</v>
@@ -1393,13 +1393,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D74" t="n" s="0">
         <v>0.0</v>
@@ -1407,13 +1407,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D75" t="n" s="0">
         <v>0.0</v>
@@ -1421,13 +1421,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D77" t="n" s="0">
         <v>0.0</v>
@@ -1449,13 +1449,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>18.0</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>18.0</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>18.0</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>18.0</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>18.0</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1589,15 +1589,29 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B88" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
+      <c r="B89" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,7 +1644,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
     <t>2026-04-12</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-04-13</t>
   </si>
   <si>
@@ -290,6 +275,27 @@
   </si>
   <si>
     <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +393,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>1.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,10 +405,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -413,10 +419,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -427,10 +433,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -441,7 +447,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>20.0</v>
@@ -455,7 +461,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>20.0</v>
@@ -469,7 +475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>20.0</v>
@@ -483,7 +489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>20.0</v>
@@ -497,7 +503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>20.0</v>
@@ -511,7 +517,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>20.0</v>
@@ -525,7 +531,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>20.0</v>
@@ -539,7 +545,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>20.0</v>
@@ -553,10 +559,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -567,10 +573,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -581,10 +587,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -595,10 +601,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -609,10 +615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -623,10 +629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -637,7 +643,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>19.0</v>
@@ -651,7 +657,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>19.0</v>
@@ -665,7 +671,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>19.0</v>
@@ -679,7 +685,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>19.0</v>
@@ -693,7 +699,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>19.0</v>
@@ -707,10 +713,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -721,10 +727,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -735,10 +741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -749,10 +755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -763,10 +769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -777,10 +783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -791,10 +797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,13 +811,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D32" t="n" s="0">
         <v>0.0</v>
@@ -819,13 +825,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" t="n" s="0">
         <v>0.0</v>
@@ -833,13 +839,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D34" t="n" s="0">
         <v>0.0</v>
@@ -847,13 +853,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" t="n" s="0">
         <v>0.0</v>
@@ -861,13 +867,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D36" t="n" s="0">
         <v>0.0</v>
@@ -875,13 +881,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" t="n" s="0">
         <v>0.0</v>
@@ -889,10 +895,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -903,10 +909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -917,10 +923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -931,10 +937,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -945,10 +951,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -959,10 +965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -973,10 +979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -987,7 +993,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>17.0</v>
@@ -1001,10 +1007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1015,10 +1021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1029,10 +1035,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>1.0</v>
@@ -1043,10 +1049,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>1.0</v>
@@ -1057,10 +1063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>1.0</v>
@@ -1071,10 +1077,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>1.0</v>
@@ -1085,7 +1091,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>18.0</v>
@@ -1099,10 +1105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1113,10 +1119,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1127,10 +1133,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1141,7 +1147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>18.0</v>
@@ -1155,7 +1161,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>18.0</v>
@@ -1169,7 +1175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>18.0</v>
@@ -1183,10 +1189,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
@@ -1197,10 +1203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
@@ -1211,10 +1217,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>1.0</v>
@@ -1225,7 +1231,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>18.0</v>
@@ -1239,7 +1245,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>18.0</v>
@@ -1253,7 +1259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>18.0</v>
@@ -1267,7 +1273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>18.0</v>
@@ -1281,7 +1287,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>18.0</v>
@@ -1295,13 +1301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1309,13 +1315,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D68" t="n" s="0">
         <v>0.0</v>
@@ -1323,13 +1329,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D69" t="n" s="0">
         <v>0.0</v>
@@ -1337,13 +1343,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D70" t="n" s="0">
         <v>0.0</v>
@@ -1351,13 +1357,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D71" t="n" s="0">
         <v>0.0</v>
@@ -1365,13 +1371,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1385,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1393,10 +1399,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1413,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,7 +1427,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>18.0</v>
@@ -1435,7 +1441,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>18.0</v>
@@ -1449,7 +1455,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>18.0</v>
@@ -1463,7 +1469,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>18.0</v>
@@ -1477,7 +1483,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>18.0</v>
@@ -1491,10 +1497,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1505,10 +1511,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1519,10 +1525,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1533,10 +1539,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1547,10 +1553,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1561,10 +1567,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1575,10 +1581,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1589,10 +1595,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1603,15 +1609,29 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1627,24 +1647,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
     </row>
   </sheetData>
@@ -1659,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,33 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
     <t>2026-04-20</t>
   </si>
   <si>
@@ -296,6 +269,27 @@
   </si>
   <si>
     <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -393,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -405,7 +399,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
         <v>20.0</v>
@@ -419,7 +413,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>20.0</v>
@@ -433,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>20.0</v>
@@ -447,10 +441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -461,10 +455,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -475,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -489,10 +483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -503,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -517,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -531,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -545,10 +539,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -559,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>19.0</v>
@@ -573,7 +567,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>19.0</v>
@@ -587,7 +581,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>19.0</v>
@@ -601,10 +595,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -615,10 +609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -629,10 +623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -643,10 +637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -657,10 +651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -671,10 +665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -685,10 +679,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -699,13 +693,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D24" t="n" s="0">
         <v>0.0</v>
@@ -713,13 +707,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D25" t="n" s="0">
         <v>0.0</v>
@@ -727,13 +721,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D26" t="n" s="0">
         <v>0.0</v>
@@ -741,13 +735,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D27" t="n" s="0">
         <v>0.0</v>
@@ -755,13 +749,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D28" t="n" s="0">
         <v>0.0</v>
@@ -769,13 +763,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>0.0</v>
@@ -783,13 +777,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D30" t="n" s="0">
         <v>0.0</v>
@@ -797,13 +791,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D31" t="n" s="0">
         <v>0.0</v>
@@ -811,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -825,10 +819,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -839,10 +833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -853,10 +847,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -867,10 +861,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -881,10 +875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -895,10 +889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>1.0</v>
@@ -909,10 +903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -923,10 +917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -937,10 +931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -951,10 +945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>1.0</v>
@@ -965,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>1.0</v>
@@ -979,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>1.0</v>
@@ -993,7 +987,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>17.0</v>
@@ -1007,10 +1001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1021,10 +1015,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1035,7 +1029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>18.0</v>
@@ -1049,7 +1043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>18.0</v>
@@ -1063,7 +1057,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>18.0</v>
@@ -1077,7 +1071,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>18.0</v>
@@ -1091,7 +1085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>18.0</v>
@@ -1105,10 +1099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>1.0</v>
@@ -1119,10 +1113,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>1.0</v>
@@ -1133,10 +1127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>1.0</v>
@@ -1147,7 +1141,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>18.0</v>
@@ -1161,7 +1155,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>18.0</v>
@@ -1175,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>18.0</v>
@@ -1189,13 +1183,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D59" t="n" s="0">
         <v>0.0</v>
@@ -1203,13 +1197,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D60" t="n" s="0">
         <v>0.0</v>
@@ -1217,13 +1211,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1231,13 +1225,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1245,13 +1239,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D63" t="n" s="0">
         <v>0.0</v>
@@ -1259,13 +1253,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D64" t="n" s="0">
         <v>0.0</v>
@@ -1273,13 +1267,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D65" t="n" s="0">
         <v>0.0</v>
@@ -1287,13 +1281,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D66" t="n" s="0">
         <v>0.0</v>
@@ -1301,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1315,10 +1309,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1329,10 +1323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1343,7 +1337,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>18.0</v>
@@ -1357,7 +1351,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>18.0</v>
@@ -1371,7 +1365,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>18.0</v>
@@ -1385,10 +1379,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1399,10 +1393,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1413,10 +1407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1427,10 +1421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1441,10 +1435,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1455,10 +1449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1469,10 +1463,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1483,10 +1477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1497,10 +1491,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1511,10 +1505,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1525,10 +1519,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1539,7 +1533,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>17.0</v>
@@ -1553,7 +1547,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>17.0</v>
@@ -1567,7 +1561,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>17.0</v>
@@ -1581,7 +1575,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>17.0</v>
@@ -1595,7 +1589,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>17.0</v>
@@ -1609,7 +1603,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" t="n" s="0">
         <v>17.0</v>
@@ -1618,20 +1612,6 @@
         <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1647,21 +1627,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>17.0</v>
@@ -1679,18 +1659,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
     <t>2026-04-26</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-04-27</t>
   </si>
   <si>
@@ -290,6 +275,27 @@
   </si>
   <si>
     <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +393,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>0.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,10 +405,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -413,10 +419,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -427,10 +433,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -441,7 +447,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>19.0</v>
@@ -455,7 +461,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>19.0</v>
@@ -469,7 +475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>19.0</v>
@@ -483,7 +489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>19.0</v>
@@ -497,7 +503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>19.0</v>
@@ -511,10 +517,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -525,10 +531,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -539,10 +545,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -553,10 +559,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -567,10 +573,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -581,10 +587,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -595,10 +601,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -609,13 +615,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D18" t="n" s="0">
         <v>0.0</v>
@@ -623,13 +629,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D19" t="n" s="0">
         <v>0.0</v>
@@ -637,13 +643,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D20" t="n" s="0">
         <v>0.0</v>
@@ -651,13 +657,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D21" t="n" s="0">
         <v>0.0</v>
@@ -665,13 +671,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>0.0</v>
@@ -679,13 +685,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D23" t="n" s="0">
         <v>0.0</v>
@@ -693,10 +699,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -707,10 +713,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -721,10 +727,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -735,10 +741,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -749,10 +755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -763,10 +769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -777,10 +783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -791,7 +797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>17.0</v>
@@ -805,10 +811,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -819,10 +825,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>1.0</v>
@@ -833,10 +839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>1.0</v>
@@ -847,10 +853,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>1.0</v>
@@ -861,10 +867,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>1.0</v>
@@ -875,10 +881,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>1.0</v>
@@ -889,7 +895,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>18.0</v>
@@ -903,10 +909,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -917,10 +923,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -931,10 +937,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -945,7 +951,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>18.0</v>
@@ -959,7 +965,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>18.0</v>
@@ -973,7 +979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>18.0</v>
@@ -987,10 +993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>1.0</v>
@@ -1001,10 +1007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>1.0</v>
@@ -1015,10 +1021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
@@ -1029,7 +1035,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>18.0</v>
@@ -1043,7 +1049,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>18.0</v>
@@ -1057,7 +1063,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>18.0</v>
@@ -1071,7 +1077,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>18.0</v>
@@ -1085,7 +1091,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>18.0</v>
@@ -1099,13 +1105,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D53" t="n" s="0">
         <v>0.0</v>
@@ -1113,13 +1119,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D54" t="n" s="0">
         <v>0.0</v>
@@ -1127,13 +1133,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D55" t="n" s="0">
         <v>0.0</v>
@@ -1141,13 +1147,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D56" t="n" s="0">
         <v>0.0</v>
@@ -1155,13 +1161,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D57" t="n" s="0">
         <v>0.0</v>
@@ -1169,13 +1175,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D58" t="n" s="0">
         <v>0.0</v>
@@ -1183,10 +1189,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1197,10 +1203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1211,10 +1217,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,7 +1231,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>18.0</v>
@@ -1239,7 +1245,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>18.0</v>
@@ -1253,7 +1259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>18.0</v>
@@ -1267,7 +1273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>18.0</v>
@@ -1281,7 +1287,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>18.0</v>
@@ -1295,10 +1301,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,10 +1315,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1323,10 +1329,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1337,10 +1343,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1351,10 +1357,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1365,10 +1371,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1385,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1393,10 +1399,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1413,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,7 +1427,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>17.0</v>
@@ -1435,7 +1441,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>17.0</v>
@@ -1449,7 +1455,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>17.0</v>
@@ -1463,7 +1469,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>17.0</v>
@@ -1477,7 +1483,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>17.0</v>
@@ -1491,7 +1497,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>17.0</v>
@@ -1505,7 +1511,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>17.0</v>
@@ -1519,7 +1525,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>17.0</v>
@@ -1533,7 +1539,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>17.0</v>
@@ -1547,7 +1553,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>17.0</v>
@@ -1561,7 +1567,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>17.0</v>
@@ -1575,7 +1581,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>17.0</v>
@@ -1589,7 +1595,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>17.0</v>
@@ -1603,7 +1609,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
         <v>17.0</v>
@@ -1612,6 +1618,20 @@
         <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1627,21 +1647,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>17.0</v>
@@ -1659,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="105">
   <si>
     <t>Date</t>
   </si>
@@ -28,39 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-26</t>
+    <t>2026-05-05</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
     <t>2026-05-06</t>
   </si>
   <si>
@@ -296,6 +269,39 @@
   </si>
   <si>
     <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -407,11 +413,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -422,7 +428,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -436,7 +442,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -450,7 +456,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -464,7 +470,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -478,7 +484,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -492,10 +498,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -506,10 +512,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D10" t="n" s="0">
         <v>0.0</v>
@@ -520,10 +526,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" t="n" s="0">
         <v>0.0</v>
@@ -534,10 +540,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" t="n" s="0">
         <v>0.0</v>
@@ -548,10 +554,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D13" t="n" s="0">
         <v>0.0</v>
@@ -562,10 +568,10 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D14" t="n" s="0">
         <v>0.0</v>
@@ -576,10 +582,10 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D15" t="n" s="0">
         <v>0.0</v>
@@ -590,10 +596,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D16" t="n" s="0">
         <v>0.0</v>
@@ -604,10 +610,10 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D17" t="n" s="0">
         <v>0.0</v>
@@ -618,7 +624,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -632,7 +638,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -646,7 +652,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -660,7 +666,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -674,7 +680,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -688,7 +694,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -702,7 +708,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -716,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>1.0</v>
@@ -730,7 +736,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>1.0</v>
@@ -744,7 +750,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>1.0</v>
@@ -758,7 +764,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>1.0</v>
@@ -772,7 +778,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>1.0</v>
@@ -814,7 +820,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -912,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>1.0</v>
@@ -926,7 +932,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>1.0</v>
@@ -940,7 +946,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>1.0</v>
@@ -982,10 +988,10 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D44" t="n" s="0">
         <v>0.0</v>
@@ -996,10 +1002,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D45" t="n" s="0">
         <v>0.0</v>
@@ -1010,10 +1016,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D46" t="n" s="0">
         <v>0.0</v>
@@ -1027,7 +1033,7 @@
         <v>18.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D47" t="n" s="0">
         <v>0.0</v>
@@ -1041,7 +1047,7 @@
         <v>18.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>0.0</v>
@@ -1055,7 +1061,7 @@
         <v>18.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D49" t="n" s="0">
         <v>0.0</v>
@@ -1069,7 +1075,7 @@
         <v>18.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1083,7 +1089,7 @@
         <v>18.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1097,7 +1103,7 @@
         <v>18.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D52" t="n" s="0">
         <v>0.0</v>
@@ -1108,7 +1114,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1122,7 +1128,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1136,7 +1142,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1178,7 +1184,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1192,7 +1198,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1206,7 +1212,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1220,7 +1226,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1234,7 +1240,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1248,7 +1254,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1262,7 +1268,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1276,7 +1282,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1290,7 +1296,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1304,7 +1310,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1318,7 +1324,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1332,7 +1338,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1514,7 +1520,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1528,7 +1534,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1542,7 +1548,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1556,7 +1562,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1570,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1584,7 +1590,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1598,7 +1604,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1612,7 +1618,7 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
@@ -1626,13 +1632,41 @@
         <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C90" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D90" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D92" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,24 +1681,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
@@ -1679,18 +1713,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,36 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-05</t>
+    <t>2026-05-13</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
     <t>2026-05-14</t>
   </si>
   <si>
@@ -302,6 +278,27 @@
   </si>
   <si>
     <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
   </si>
   <si>
     <t>Reason</t>
@@ -378,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -413,11 +410,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -428,10 +425,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -442,10 +439,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -456,10 +453,10 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -470,10 +467,10 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>0.0</v>
@@ -484,10 +481,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -498,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -512,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -526,7 +523,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -540,7 +537,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -554,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -568,7 +565,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -582,7 +579,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -596,7 +593,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -610,7 +607,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -624,7 +621,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -638,7 +635,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>1.0</v>
@@ -652,7 +649,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -666,7 +663,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -694,7 +691,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -708,7 +705,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -792,7 +789,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>1.0</v>
@@ -806,7 +803,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>1.0</v>
@@ -820,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>1.0</v>
@@ -876,10 +873,10 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D36" t="n" s="0">
         <v>0.0</v>
@@ -890,10 +887,10 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" t="n" s="0">
         <v>0.0</v>
@@ -904,10 +901,10 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D38" t="n" s="0">
         <v>0.0</v>
@@ -921,7 +918,7 @@
         <v>18.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D39" t="n" s="0">
         <v>0.0</v>
@@ -935,7 +932,7 @@
         <v>18.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D40" t="n" s="0">
         <v>0.0</v>
@@ -949,7 +946,7 @@
         <v>18.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D41" t="n" s="0">
         <v>0.0</v>
@@ -963,7 +960,7 @@
         <v>18.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D42" t="n" s="0">
         <v>0.0</v>
@@ -977,7 +974,7 @@
         <v>18.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D43" t="n" s="0">
         <v>0.0</v>
@@ -988,7 +985,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -1002,7 +999,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1016,7 +1013,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1072,7 +1069,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1086,7 +1083,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1100,7 +1097,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1114,7 +1111,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1128,7 +1125,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1142,7 +1139,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1156,7 +1153,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1170,7 +1167,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1184,7 +1181,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1198,7 +1195,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1212,7 +1209,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1408,7 +1405,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1422,7 +1419,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1436,7 +1433,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1450,7 +1447,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1464,7 +1461,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1478,7 +1475,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1492,7 +1489,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1506,7 +1503,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1520,7 +1517,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1534,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1548,7 +1545,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1562,7 +1559,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1576,7 +1573,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1590,7 +1587,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1604,7 +1601,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1618,7 +1615,7 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
@@ -1632,7 +1629,7 @@
         <v>93</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C90" t="n" s="0">
         <v>0.0</v>
@@ -1646,26 +1643,12 @@
         <v>94</v>
       </c>
       <c r="B91" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C91" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="B92" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="C92" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D92" t="s" s="0">
         <v>5</v>
       </c>
     </row>
@@ -1681,24 +1664,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>100</v>
-      </c>
       <c r="C2" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>103</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,30 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-13</t>
+    <t>2026-05-19</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
     <t>2026-05-20</t>
   </si>
   <si>
@@ -299,6 +281,15 @@
   </si>
   <si>
     <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
   </si>
   <si>
     <t>Reason</t>
@@ -375,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,11 +401,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -425,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -439,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -453,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -467,7 +458,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -495,7 +486,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>1.0</v>
@@ -509,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -523,7 +514,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -537,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -551,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -565,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>1.0</v>
@@ -593,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -607,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -621,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -677,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>1.0</v>
@@ -691,7 +682,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>1.0</v>
@@ -705,7 +696,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>1.0</v>
@@ -789,10 +780,10 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D30" t="n" s="0">
         <v>0.0</v>
@@ -803,10 +794,10 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D31" t="n" s="0">
         <v>0.0</v>
@@ -817,10 +808,10 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D32" t="n" s="0">
         <v>0.0</v>
@@ -834,7 +825,7 @@
         <v>18.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D33" t="n" s="0">
         <v>0.0</v>
@@ -848,7 +839,7 @@
         <v>18.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" t="n" s="0">
         <v>0.0</v>
@@ -862,7 +853,7 @@
         <v>18.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D35" t="n" s="0">
         <v>0.0</v>
@@ -873,7 +864,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -887,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -901,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -985,7 +976,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -999,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1013,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1027,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1041,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1055,7 +1046,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1069,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1083,7 +1074,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1097,7 +1088,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1321,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1335,7 +1326,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1349,7 +1340,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1363,7 +1354,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1377,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1391,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1419,7 +1410,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1433,7 +1424,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1447,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1461,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1475,7 +1466,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1489,7 +1480,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1503,7 +1494,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1517,7 +1508,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1531,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1545,7 +1536,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1559,7 +1550,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1573,7 +1564,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1587,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1601,55 +1592,13 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1664,24 +1613,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -1696,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
   </si>
   <si>
@@ -290,6 +269,27 @@
   </si>
   <si>
     <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -413,10 +413,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -427,10 +427,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -441,10 +441,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>1.0</v>
@@ -455,10 +455,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>1.0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>18.0</v>
@@ -497,10 +497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -525,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>18.0</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>18.0</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>18.0</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>1.0</v>
@@ -595,10 +595,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>1.0</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>1.0</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>18.0</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>18.0</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>18.0</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>18.0</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>18.0</v>
@@ -693,13 +693,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D24" t="n" s="0">
         <v>0.0</v>
@@ -707,13 +707,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D25" t="n" s="0">
         <v>0.0</v>
@@ -721,13 +721,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D26" t="n" s="0">
         <v>0.0</v>
@@ -735,13 +735,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D27" t="n" s="0">
         <v>0.0</v>
@@ -749,13 +749,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D28" t="n" s="0">
         <v>0.0</v>
@@ -763,13 +763,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>0.0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,10 +805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>18.0</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>18.0</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>18.0</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>18.0</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>18.0</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>17.0</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>17.0</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>17.0</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>17.0</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>17.0</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>17.0</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>17.0</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>17.0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>17.0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>17.0</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>17.0</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>17.0</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>17.0</v>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>17.0</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>17.0</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>16.0</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1589,15 +1589,29 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B88" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
+      <c r="B89" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,7 +1644,7 @@
         <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -28,36 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
     <t>2026-06-03</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -290,6 +266,39 @@
   </si>
   <si>
     <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -387,11 +396,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>1.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -399,10 +408,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>1.0</v>
@@ -413,7 +422,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>18.0</v>
@@ -427,7 +436,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>18.0</v>
@@ -441,7 +450,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>18.0</v>
@@ -455,7 +464,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>18.0</v>
@@ -469,7 +478,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>18.0</v>
@@ -483,7 +492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>18.0</v>
@@ -497,10 +506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>1.0</v>
@@ -511,10 +520,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -525,10 +534,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -539,7 +548,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>18.0</v>
@@ -553,7 +562,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>18.0</v>
@@ -567,13 +576,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D15" t="n" s="0">
         <v>0.0</v>
@@ -581,13 +590,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D16" t="n" s="0">
         <v>0.0</v>
@@ -595,13 +604,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D17" t="n" s="0">
         <v>0.0</v>
@@ -609,13 +618,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D18" t="n" s="0">
         <v>0.0</v>
@@ -623,13 +632,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D19" t="n" s="0">
         <v>0.0</v>
@@ -637,13 +646,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" t="n" s="0">
         <v>0.0</v>
@@ -651,13 +660,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D21" t="n" s="0">
         <v>0.0</v>
@@ -665,13 +674,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>0.0</v>
@@ -679,13 +688,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>18.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D23" t="n" s="0">
         <v>0.0</v>
@@ -693,10 +702,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -707,10 +716,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -721,10 +730,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -735,7 +744,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>18.0</v>
@@ -749,7 +758,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>18.0</v>
@@ -763,10 +772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -791,10 +800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -805,10 +814,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -819,10 +828,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -833,10 +842,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -847,10 +856,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -861,10 +870,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -875,10 +884,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -903,10 +912,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -917,10 +926,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -931,7 +940,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>17.0</v>
@@ -945,7 +954,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>17.0</v>
@@ -959,7 +968,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>17.0</v>
@@ -973,7 +982,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>17.0</v>
@@ -987,7 +996,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>17.0</v>
@@ -1001,7 +1010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>17.0</v>
@@ -1015,7 +1024,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>17.0</v>
@@ -1029,7 +1038,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>17.0</v>
@@ -1043,7 +1052,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>17.0</v>
@@ -1057,7 +1066,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>17.0</v>
@@ -1071,7 +1080,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>17.0</v>
@@ -1085,7 +1094,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>17.0</v>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1127,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1141,10 +1150,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1155,10 +1164,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1169,10 +1178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1183,10 +1192,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1197,10 +1206,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1211,10 +1220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,10 +1234,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1239,10 +1248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1253,10 +1262,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1267,10 +1276,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1281,10 +1290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1295,10 +1304,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1309,10 +1318,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1323,10 +1332,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1337,10 +1346,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1351,10 +1360,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1365,10 +1374,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1379,10 +1388,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1393,10 +1402,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1407,10 +1416,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1421,10 +1430,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1435,10 +1444,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1449,10 +1458,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1463,10 +1472,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1477,10 +1486,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1519,10 +1528,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1533,10 +1542,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1547,10 +1556,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1561,10 +1570,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1575,10 +1584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1589,10 +1598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1603,16 +1612,44 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1627,24 +1664,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
@@ -1659,18 +1696,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Video-Indexing.xlsx
+++ b/gsc-export/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,39 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-03</t>
+    <t>2026-06-12</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>2026-06-07</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
     <t>2026-06-13</t>
   </si>
   <si>
@@ -299,6 +272,27 @@
   </si>
   <si>
     <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>Reason</t>
@@ -375,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,11 +404,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>1.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -424,11 +418,11 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>1.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -453,10 +447,10 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>0.0</v>
@@ -467,10 +461,10 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>0.0</v>
@@ -481,10 +475,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -498,7 +492,7 @@
         <v>18.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -512,7 +506,7 @@
         <v>18.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D10" t="n" s="0">
         <v>0.0</v>
@@ -526,7 +520,7 @@
         <v>18.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D11" t="n" s="0">
         <v>0.0</v>
@@ -540,7 +534,7 @@
         <v>18.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D12" t="n" s="0">
         <v>0.0</v>
@@ -554,7 +548,7 @@
         <v>18.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D13" t="n" s="0">
         <v>0.0</v>
@@ -568,7 +562,7 @@
         <v>18.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D14" t="n" s="0">
         <v>0.0</v>
@@ -579,7 +573,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -593,7 +587,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -607,7 +601,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -649,7 +643,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -663,7 +657,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -677,7 +671,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -691,7 +685,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -705,7 +699,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -719,7 +713,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -733,7 +727,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -747,7 +741,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -761,7 +755,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -775,7 +769,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -789,7 +783,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -803,7 +797,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -985,7 +979,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -999,7 +993,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1013,7 +1007,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1027,7 +1021,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1041,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1055,7 +1049,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1069,7 +1063,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1083,7 +1077,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1097,7 +1091,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1111,7 +1105,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1125,7 +1119,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1139,7 +1133,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1153,7 +1147,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1167,7 +1161,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1181,7 +1175,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1195,7 +1189,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1209,7 +1203,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1223,7 +1217,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1237,7 +1231,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1251,7 +1245,7 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1265,7 +1259,7 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1279,7 +1273,7 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1293,7 +1287,7 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1307,7 +1301,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1321,7 +1315,7 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1335,7 +1329,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1349,7 +1343,7 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1363,7 +1357,7 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1377,7 +1371,7 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1391,7 +1385,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1405,7 +1399,7 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1419,7 +1413,7 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1433,7 +1427,7 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1447,7 +1441,7 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1461,7 +1455,7 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1475,7 +1469,7 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1489,7 +1483,7 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1503,7 +1497,7 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1517,7 +1511,7 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1531,7 +1525,7 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1545,7 +1539,7 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1559,7 +1553,7 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1573,7 +1567,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1587,7 +1581,7 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
@@ -1601,7 +1595,7 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>0.0</v>
@@ -1615,41 +1609,13 @@
         <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="C89" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D91" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1664,24 +1630,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
@@ -1696,18 +1662,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
